--- a/docs/chatgpt_tariffs.xlsx
+++ b/docs/chatgpt_tariffs.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT Plus" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT Pro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ChatGPT Plus" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ChatGPT Pro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ChatGPT Plus'!$A$1:$F$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ChatGPT Pro'!$A$1:$F$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ChatGPT Pro'!$A$1:$F$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3790,7 +3790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -3836,125 +3836,123 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5979732</t>
+          <t>https://plati.market/itm/5422669</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LevelX DZ</t>
+          <t>SpicyCheeze</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 1 месяц – Совместный аккаунт | Безопасный и надёжный доступ</t>
+          <t>1 - Месяц | PRO | Без Gemini</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>467</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>1104</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4125885</t>
+          <t>https://plati.market/itm/5979732</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Будни Дизайнера</t>
+          <t>LevelX DZ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PRO X5</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT Pro 1 месяц – Совместный аккаунт | Безопасный и надёжный доступ</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>8590</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6031453</t>
+          <t>https://plati.market/itm/4125885</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SiberAI</t>
+          <t>Будни Дизайнера</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 5X 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>59</v>
+          <t>PRO X5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>9000</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5143806</t>
+          <t>https://plati.market/itm/6031453</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CorzySell</t>
+          <t>SiberAI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pro x5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Активация/Продление ChatGPT Pro 5X 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>59</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9099</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5912754</t>
+          <t>https://plati.market/itm/5143806</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SiberiaPlay</t>
+          <t>CorzySell</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
+          <t>Pro x5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3966,23 +3964,23 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>9300</v>
+        <v>9099</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5636225</t>
+          <t>https://plati.market/itm/5912754</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NNStore</t>
+          <t>SiberiaPlay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chat GPT PRO x5 | CODEX - Готовый аккаунт</t>
+          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3991,26 +3989,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>9331</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5734457</t>
+          <t>https://plati.market/itm/5636225</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KABAN STORE</t>
+          <t>NNStore</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3. [АКЦИЯ] ChatGPT Pro X5 1 МЕСЯЦ l Подписка / Продление (на Ваш аккаунт, без входа, за минуту)</t>
+          <t>Chat GPT PRO x5 | CODEX - Готовый аккаунт</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4019,26 +4017,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>9379</v>
+        <v>9331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5896950</t>
+          <t>https://plati.market/itm/5734457</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SiberiaPlay</t>
+          <t>KABAN STORE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
+          <t>3. [АКЦИЯ] ChatGPT Pro X5 1 МЕСЯЦ l Подписка / Продление (на Ваш аккаунт, без входа, за минуту)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4047,26 +4045,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9388</v>
+        <v>9379</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5785342</t>
+          <t>https://plati.market/itm/5896950</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Geniya</t>
+          <t>SiberiaPlay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24/7 АВТО | Chat gpt PRO Х5 1 МЕСЯЦ Активация/продление (На ваш аккаунт без входа за минуту)</t>
+          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4078,161 +4076,161 @@
         <v>2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9399</v>
+        <v>9388</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6041416</t>
+          <t>https://plati.market/itm/5785342</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PAYFLIX</t>
+          <t>Geniya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[24/7 АВТОВЫДАЧА] Chat GPT PRO 5X | АКТИВАЦИЯ / ПРОДЛЕНИЕ | 1 МЕСЯЦ | БЕЗ ВХОДА | ВАШ АККАУНТ</t>
+          <t>24/7 АВТО | Chat gpt PRO Х5 1 МЕСЯЦ Активация/продление (На ваш аккаунт без входа за минуту)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9499</v>
+        <v>9399</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3521831</t>
+          <t>https://plati.market/itm/6041416</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>tahonya</t>
+          <t>PAYFLIX</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PRO X5 НА МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>69</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
+          <t>[24/7 АВТОВЫДАЧА] Chat GPT PRO 5X | АКТИВАЦИЯ / ПРОДЛЕНИЕ | 1 МЕСЯЦ | БЕЗ ВХОДА | ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>9600</v>
+        <v>9499</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5218986</t>
+          <t>https://plati.market/itm/3521831</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>northernlights</t>
+          <t>tahonya</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5x</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>&gt;50</t>
-        </is>
+          <t>PRO X5 НА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>69</v>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>9633</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5856306</t>
+          <t>https://plati.market/itm/5218986</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GameLootGG</t>
+          <t>northernlights</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 - 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>65</v>
+          <t>ChatGPT Pro 5x</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>&gt;50</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>9638</v>
+        <v>9633</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6051702</t>
+          <t>https://plati.market/itm/5856306</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KappaStore</t>
+          <t>GameLootGG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 - 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>9839</v>
+        <v>9638</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4306654</t>
+          <t>https://plati.market/itm/6051702</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fursov.me</t>
+          <t>KappaStore</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3. Продление ChatGPT PRO X5 — 1 МЕСЯЦ | На Ваш аккаунт | Оф.Метод</t>
+          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4241,26 +4239,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9949</v>
+        <v>9839</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5834250</t>
+          <t>https://plati.market/itm/4306654</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KappaStore</t>
+          <t>fursov.me</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
+          <t>3. Продление ChatGPT PRO X5 — 1 МЕСЯЦ | На Ваш аккаунт | Оф.Метод</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4269,72 +4267,74 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>9969</v>
+        <v>9949</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5995043</t>
+          <t>https://plati.market/itm/5834250</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ImSubscribed</t>
+          <t>KappaStore</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ChatGPT Pro x5 1 месяц</t>
+          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9989</v>
+        <v>9969</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4695121</t>
+          <t>https://plati.market/itm/5995043</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DigiSelling</t>
+          <t>ImSubscribed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Подписка PRO x5  1 месяц</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>61</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2</v>
+          <t>ChatGPT Pro x5 1 месяц</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9990</v>
+        <v>9989</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5162565</t>
+          <t>https://plati.market/itm/4695121</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4344,14 +4344,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Оформление подписки PRO на ваш аккаунт</t>
+          <t>Подписка PRO x5  1 месяц</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>9990</v>
@@ -4360,45 +4360,43 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5352918</t>
+          <t>https://plati.market/itm/5162565</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>forYou97</t>
+          <t>DigiSelling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2. Активация/Продление ChatGPT Pro x5 1 МЕСЯЦ (на ваш аккаунт, быстро, без входа))</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Оформление подписки PRO на ваш аккаунт</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>9999</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4339002</t>
+          <t>https://plati.market/itm/5352918</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>forYou97</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>7. [Скидка] ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+          <t>2. Активация/Продление ChatGPT Pro x5 1 МЕСЯЦ (на ваш аккаунт, быстро, без входа))</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4406,10 +4404,8 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+      <c r="E22" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>9999</v>
@@ -4418,24 +4414,28 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5407372</t>
+          <t>https://plati.market/itm/4339002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>STORE_IZI</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>21</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
+          <t>7. [Скидка] ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F23" s="3" t="n">
         <v>9999</v>
@@ -4444,35 +4444,33 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3218237</t>
+          <t>https://plati.market/itm/5407372</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>STORE_IZI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PRO X5 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>21</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>10064</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3235033</t>
+          <t>https://plati.market/itm/3218237</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4482,7 +4480,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT PRO X5 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
+          <t>PRO X5 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4491,26 +4489,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10078</v>
+        <v>10064</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4371645</t>
+          <t>https://plati.market/itm/3235033</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MyKEYS</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x - 1 месяц (5.6)</t>
+          <t>Активация/Продление ChatGPT PRO X5 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4519,142 +4517,142 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>10199</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5992061</t>
+          <t>https://plati.market/itm/4371645</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kernel_JX</t>
+          <t>MyKEYS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[АВТО 24/7 ] ChatGPT PRO 5X 1 месяц | АКТИВАЦИЯ / ПРОДЛЕНИЕ ( без логина, на ваш аккаунт)</t>
+          <t>ChatGPT PRO 5x - 1 месяц (5.6)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>14</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10273</v>
+        <v>10199</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3725372</t>
+          <t>https://plati.market/itm/5992061</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>Kernel_JX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>АВТО 24/7| Активация/ Продление CHATGPT PRO X5 на 1 месяц (Ваш аккаунт, без логина) ГАРАНТИЯ 1 МЕСЯЦ</t>
+          <t>[АВТО 24/7 ] ChatGPT PRO 5X 1 месяц | АКТИВАЦИЯ / ПРОДЛЕНИЕ ( без логина, на ваш аккаунт)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>25</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>10401</v>
+        <v>10273</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6021924</t>
+          <t>https://plati.market/itm/3725372</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VEYRO</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ ChatGPT Pro X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+          <t>АВТО 24/7| Активация/ Продление CHATGPT PRO X5 на 1 месяц (Ваш аккаунт, без логина) ГАРАНТИЯ 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>25</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10499</v>
+        <v>10401</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4802730</t>
+          <t>https://plati.market/itm/6021924</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>northernlights</t>
+          <t>VEYRO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Подписка ChatGPT Pro 5x</t>
+          <t>АКТИВАЦИЯ ChatGPT Pro X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>35</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>10591</v>
+        <v>10499</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4380086</t>
+          <t>https://plati.market/itm/4802730</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MyKEYS</t>
+          <t>northernlights</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x - 1 месяц (5.5)</t>
+          <t>Подписка ChatGPT Pro 5x</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4663,26 +4661,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10599</v>
+        <v>10591</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3705934</t>
+          <t>https://plati.market/itm/4380086</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>hayta</t>
+          <t>MyKEYS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3. 24/7 АВТО | ChatGPT PRO X5 1 МЕСЯЦ | Подписка (на Ваш аккаунт, без входа, за минуту)</t>
+          <t>ChatGPT PRO 5x - 1 месяц (5.5)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4691,26 +4689,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>10735</v>
+        <v>10599</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5794510</t>
+          <t>https://plati.market/itm/3705934</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BuyForGame</t>
+          <t>hayta</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[БЕЗ ВХОДА] АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | ЗА МИНУТУ | НА ВАШ АККАУНТ |</t>
+          <t>3. 24/7 АВТО | ChatGPT PRO X5 1 МЕСЯЦ | Подписка (на Ваш аккаунт, без входа, за минуту)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4719,65 +4717,65 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>10899</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5214484</t>
+          <t>https://plati.market/itm/5794510</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>BuyForGame</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] на 1 месяц – активация на ваш аккаунт (с передачей логина и пароля, со входом)</t>
+          <t>[БЕЗ ВХОДА] АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | ЗА МИНУТУ | НА ВАШ АККАУНТ |</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>27</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>10999</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4313142</t>
+          <t>https://plati.market/itm/5214484</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ProSeller.inc</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2. PRO 5x (1 месяц)</t>
+          <t>[ChatGPT PRO 5x] на 1 месяц – активация на ваш аккаунт (с передачей логина и пароля, со входом)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>65</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F35" s="3" t="n">
         <v>10999</v>
@@ -4786,17 +4784,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4481462</t>
+          <t>https://plati.market/itm/4313142</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>ProSeller.inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] - купить/продлить на ваш аккаунт - 1 мес - со входом (логин+пароль) [РУЧНАЯ]</t>
+          <t>2. PRO 5x (1 месяц)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4805,26 +4803,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>11199</v>
+        <v>10999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5807701</t>
+          <t>https://plati.market/itm/4481462</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mahoraga borz</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Продление \ ChatGPT Pro x5 на 1 месяц (на ваш аккаунт, без входа в аккаунт)</t>
+          <t>[ChatGPT PRO 5x] - купить/продлить на ваш аккаунт - 1 мес - со входом (логин+пароль) [РУЧНАЯ]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4833,138 +4831,138 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>11205</v>
+        <v>11199</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5980351</t>
+          <t>https://plati.market/itm/5807701</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>IGROKLAD</t>
+          <t>Mahoraga borz</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ChatGPT PRO [ НА 1 МЕСЯЦ ]</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
+          <t>Продление \ ChatGPT Pro x5 на 1 месяц (на ваш аккаунт, без входа в аккаунт)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>11345</v>
+        <v>11205</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3859725</t>
+          <t>https://plati.market/itm/5980351</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>fursov.me</t>
+          <t>IGROKLAD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GPT PRO X5 &gt;&gt; Новый аккаунт + Почта (1 месяц)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT PRO [ НА 1 МЕСЯЦ ]</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>11349</v>
+        <v>11345</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6063721</t>
+          <t>https://plati.market/itm/3859725</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MORPHEUSINTELLIGENCE</t>
+          <t>fursov.me</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5X</t>
+          <t>GPT PRO X5 &gt;&gt; Новый аккаунт + Почта (1 месяц)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>54</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>11390</v>
+        <v>11349</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3648532</t>
+          <t>https://plati.market/itm/6063721</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UgolokH</t>
+          <t>MORPHEUSINTELLIGENCE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PRO X5</t>
+          <t>ChatGPT Pro 5X</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>11490</v>
+        <v>11390</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5481303</t>
+          <t>https://plati.market/itm/3648532</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>UgolokH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 1 месяц (код активации)</t>
+          <t>PRO X5</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4972,115 +4970,113 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+      <c r="E42" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>11749</v>
+        <v>11490</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5424895</t>
+          <t>https://plati.market/itm/5481303</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AppStops</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pro подписка на месяц</t>
+          <t>ChatGPT PRO X5 1 месяц (код активации)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>11790</v>
+        <v>11749</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6055394</t>
+          <t>https://plati.market/itm/5424895</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MisterHeisenberg</t>
+          <t>AppStops</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT PRO x5 1 МЕСЯЦ на ваш аккаунт</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
+          <t>Pro подписка на месяц</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>11800</v>
+        <v>11790</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4339392</t>
+          <t>https://plati.market/itm/6055394</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MARCEL VPN</t>
+          <t>MisterHeisenberg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2.АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Pro X5 — 1 МЕСЯЦ |  НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Активация/Продление ChatGPT PRO x5 1 МЕСЯЦ на ваш аккаунт</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>11889</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4756087</t>
+          <t>https://plati.market/itm/4339392</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IronMarvell</t>
+          <t>MARCEL VPN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x 1 месяц</t>
+          <t>2.АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Pro X5 — 1 МЕСЯЦ |  НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5088,353 +5084,357 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>11990</v>
+        <v>11889</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4616358</t>
+          <t>https://plati.market/itm/4756087</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>IronMarvell</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] готовый аккаунт с подпиской + почта на 1 месяц</t>
+          <t>ChatGPT PRO 5x 1 месяц</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>11999</v>
+        <v>11990</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3931351</t>
+          <t>https://plati.market/itm/4616358</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>furfur</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 1 месяц x5</t>
+          <t>[ChatGPT PRO 5x] готовый аккаунт с подпиской + почта на 1 месяц</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>2</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12002</v>
+        <v>11999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6063473</t>
+          <t>https://plati.market/itm/3931351</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>of_existence</t>
+          <t>furfur</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
+          <t>ChatGPT PRO 1 месяц x5</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12068</v>
+        <v>12002</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4853415</t>
+          <t>https://plati.market/itm/6063473</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Super Man</t>
+          <t>of_existence</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12100</v>
+        <v>12068</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5361993</t>
+          <t>https://plati.market/itm/4853415</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZaruBot</t>
+          <t>Super Man</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x 1 месяц {Для старых и новых (обеих) учетных записей {Продление}</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>24</v>
+          <t>ChatGPT PRO X5</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>12269</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5865073</t>
+          <t>https://plati.market/itm/5361993</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Genixai</t>
+          <t>ZaruBot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4: ChatGPT Pro 5X | Активация на ваш Email | Высокие лимиты | Полная гарантия</t>
+          <t>ChatGPT PRO 5x 1 месяц {Для старых и новых (обеих) учетных записей {Продление}</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>12279</v>
+        <v>12269</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5931604</t>
+          <t>https://plati.market/itm/5865073</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MrKronos</t>
+          <t>Genixai</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x</t>
+          <t>4: ChatGPT Pro 5X | Активация на ваш Email | Высокие лимиты | Полная гарантия</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>12290</v>
+        <v>12279</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5849306</t>
+          <t>https://plati.market/itm/5931604</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JensenLoantos</t>
+          <t>MrKronos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ChatGPT Pro на 1 месяц без входа в систему</t>
+          <t>ChatGPT PRO 5x</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>12318</v>
+        <v>12290</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4362367</t>
+          <t>https://plati.market/itm/5849306</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AccountBroker</t>
+          <t>JensenLoantos</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.Активация/Продление ChatGPT Pro 5x 1 МЕСЯЦ (Без входа с использованием файлов cookie)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT Pro на 1 месяц без входа в систему</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>12469</v>
+        <v>12318</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5897564</t>
+          <t>https://plati.market/itm/4362367</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ai_Box</t>
+          <t>AccountBroker</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pro 5X [ ЛУЧШАЯ ЦЕНА ]</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>121</v>
-      </c>
-      <c r="E56" t="n">
-        <v>7</v>
+          <t>3.Активация/Продление ChatGPT Pro 5x 1 МЕСЯЦ (Без входа с использованием файлов cookie)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>12584</v>
+        <v>12469</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3683609</t>
+          <t>https://plati.market/itm/5897564</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>_RenS_</t>
+          <t>Ai_Box</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>У меня уже есть аккаунт ChatGPT (оформляется подписка Pro без входа в аккаунт)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Pro 5X [ ЛУЧШАЯ ЦЕНА ]</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>121</v>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>12609</v>
+        <v>12584</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6057697</t>
+          <t>https://plati.market/itm/3683609</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SubVault</t>
+          <t>_RenS_</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Activation/Renewal ChatGPT Pro 5X – 1 месяц | Высокие лимиты | На ваш Email | Требуется вход</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
+          <t>У меня уже есть аккаунт ChatGPT (оформляется подписка Pro без входа в аккаунт)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>12640</v>
+        <v>12609</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5960360</t>
+          <t>https://plati.market/itm/6057697</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Subverse</t>
+          <t>SubVault</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5x • Официальный доступ • Полная гарантия</t>
+          <t>Activation/Renewal ChatGPT Pro 5X – 1 месяц | Высокие лимиты | На ваш Email | Требуется вход</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -5444,49 +5444,49 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>12651</v>
+        <v>12640</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5873793</t>
+          <t>https://plati.market/itm/5960360</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>88Store AI</t>
+          <t>Subverse</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PRO x5 - 1 MONTH</t>
+          <t>ChatGPT Pro 5x • Официальный доступ • Полная гарантия</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>12717</v>
+        <v>12651</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5763830</t>
+          <t>https://plati.market/itm/5873793</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PickBest</t>
+          <t>88Store AI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chat GPT  Pro 5x | 1 Month | On your Account | Ready Account</t>
+          <t>PRO x5 - 1 MONTH</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -5496,326 +5496,324 @@
         <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>13119</v>
+        <v>12717</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6052016</t>
+          <t>https://plati.market/itm/5763830</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DigiMari</t>
+          <t>PickBest</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Активация / Продление ChatGPT PRO - 1 МЕС | ВАШ Аккаунт</t>
+          <t>Chat GPT  Pro 5x | 1 Month | On your Account | Ready Account</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>13153</v>
+        <v>13119</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5998486</t>
+          <t>https://plati.market/itm/6052016</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VantaStore</t>
+          <t>DigiMari</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ChatGPT Pro x5 - 1 месяц</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>Активация / Продление ChatGPT PRO - 1 МЕС | ВАШ Аккаунт</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>13277</v>
+        <v>13153</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3964931</t>
+          <t>https://plati.market/itm/5998486</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AI GUO GUO</t>
+          <t>VantaStore</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+          <t>ChatGPT Pro x5 - 1 месяц</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>2</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>13340</v>
+        <v>13277</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5990295</t>
+          <t>https://plati.market/itm/3964931</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PROMARKET88</t>
+          <t>AI GUO GUO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GPT PRO</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
+          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>2</v>
       </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
       <c r="F65" s="3" t="n">
-        <v>13402</v>
+        <v>13340</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5869102</t>
+          <t>https://plati.market/itm/5990295</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AI GUO GUO</t>
+          <t>PROMARKET88</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+          <t>GPT PRO</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>13512</v>
+        <v>13402</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4724944</t>
+          <t>https://plati.market/itm/5869102</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>AI GUO GUO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Без Входа)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>212</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>13667</v>
+        <v>13512</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5465686</t>
+          <t>https://plati.market/itm/4724944</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DerdoArt</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pro x5</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>54</v>
+          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Без Входа)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>14159</v>
+        <v>13667</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5688276</t>
+          <t>https://plati.market/itm/5465686</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lyutsik_Shop</t>
+          <t>DerdoArt</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CHATGPT 5.2 PRO 1 месяц ПОДПИСКА С ЗАХОДОМ НА ВАШ АККАУНТ</t>
+          <t>Pro x5</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>14229</v>
+        <v>14159</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5981988</t>
+          <t>https://plati.market/itm/5688276</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HunterGPT</t>
+          <t>Lyutsik_Shop</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 5X — 1 МЕСЯЦ (Требуется вход в аккаунт | 24/7)</t>
+          <t>CHATGPT 5.2 PRO 1 месяц ПОДПИСКА С ЗАХОДОМ НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>14326</v>
+        <v>14229</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6002830</t>
+          <t>https://plati.market/itm/5981988</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>67_Shop</t>
+          <t>HunterGPT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5X — 1 месяц | На ваш аккаунт | Без входа</t>
+          <t>Активация/Продление ChatGPT Pro 5X — 1 МЕСЯЦ (Требуется вход в аккаунт | 24/7)</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>14981</v>
+        <v>14326</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3636620</t>
+          <t>https://plati.market/itm/6002830</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>67_Shop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>4. ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
+          <t>ChatGPT PRO 5X — 1 месяц | На ваш аккаунт | Без входа</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>26654</v>
+        <v>39</v>
       </c>
       <c r="E72" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>14999</v>
+        <v>14981</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4183350</t>
+          <t>https://plati.market/itm/3636620</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SOFT_OPTOM</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CHATGPT Pro 1 месяц БЫСТРО x5</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>4. ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>26654</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>14999</v>
@@ -5824,17 +5822,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5651002</t>
+          <t>https://plati.market/itm/4183350</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>starfast</t>
+          <t>SOFT_OPTOM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ChatGPT Pro X5 - на 1 Месяц</t>
+          <t>CHATGPT Pro 1 месяц БЫСТРО x5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5846,23 +5844,23 @@
         <v>0</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>15399</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5401296</t>
+          <t>https://plati.market/itm/5651002</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>tuanbes</t>
+          <t>starfast</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
+          <t>ChatGPT Pro X5 - на 1 Месяц</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5871,292 +5869,292 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>15434</v>
+        <v>15399</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5884270</t>
+          <t>https://plati.market/itm/5401296</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ProSeller.inc</t>
+          <t>tuanbes</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2. PRO 5x (1 месяц)</t>
+          <t>ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>15799</v>
+        <v>15434</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4591665</t>
+          <t>https://plati.market/itm/5884270</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FoxyPayGlobal</t>
+          <t>ProSeller.inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pro | Месяц  | 1 участник</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>13</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
+          <t>2. PRO 5x (1 месяц)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>16049</v>
+        <v>15799</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5877715</t>
+          <t>https://plati.market/itm/4591665</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DanyCyber</t>
+          <t>FoxyPayGlobal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Активация/продление подписки ChatGPT Pro 5 раз по 1 месяц</t>
+          <t>Pro | Месяц  | 1 участник</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>16179</v>
+        <v>16049</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5437983</t>
+          <t>https://plati.market/itm/5877715</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>DanyCyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Требуется Вход)</t>
+          <t>Активация/продление подписки ChatGPT Pro 5 раз по 1 месяц</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>16246</v>
+        <v>16179</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5087858</t>
+          <t>https://plati.market/itm/5437983</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FUNFINITY SHOP</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pro 1 Месяц (x5)</t>
+          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Требуется Вход)</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>16516</v>
+        <v>16246</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5870331</t>
+          <t>https://plati.market/itm/5087858</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>karlincards</t>
+          <t>FUNFINITY SHOP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>НОВАЯ учетная запись ChatGPT PRO X5 1 МЕСЯЦ (новая учетная запись с доступом к электронной почте)</t>
+          <t>Pro 1 Месяц (x5)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>19554</v>
+        <v>16516</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5660318</t>
+          <t>https://plati.market/itm/5870331</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>sashasale</t>
+          <t>karlincards</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 20x 1 месяц (Без Входа)</t>
+          <t>НОВАЯ учетная запись ChatGPT PRO X5 1 МЕСЯЦ (новая учетная запись с доступом к электронной почте)</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>19899</v>
+        <v>19554</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5559857</t>
+          <t>https://plati.market/itm/5660318</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AltSubs</t>
+          <t>sashasale</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ChatGPT Pro - 1 месяц: новый аккаунт (полный доступ)</t>
+          <t>Активация/Продление ChatGPT Pro 20x 1 месяц (Без Входа)</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>21403</v>
+        <v>19899</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5144685</t>
+          <t>https://plati.market/itm/5559857</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>D.O.G.E. PRIME SHOP</t>
+          <t>AltSubs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pro (1 месяц)</t>
+          <t>ChatGPT Pro - 1 месяц: новый аккаунт (полный доступ)</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>21809</v>
+        <v>21403</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3714311</t>
+          <t>https://plati.market/itm/5144685</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Luxtake</t>
+          <t>D.O.G.E. PRIME SHOP</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3. 24/7 АВТО | Продление ChatGPT PRO — 1 МЕСЯЦ | На Ваш аккаунт | Без входа | За минуту</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Pro (1 месяц)</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>21975</v>
+        <v>21809</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5231895</t>
+          <t>https://plati.market/itm/3714311</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PREMIUMSTOREXYZ</t>
+          <t>Luxtake</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pro (1 месяц)</t>
+          <t>3. 24/7 АВТО | Продление ChatGPT PRO — 1 МЕСЯЦ | На Ваш аккаунт | Без входа | За минуту</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6165,172 +6163,200 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>22183</v>
+        <v>21975</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4881173</t>
+          <t>https://plati.market/itm/5231895</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Exclusive_Play</t>
+          <t>PREMIUMSTOREXYZ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pro</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>33</v>
+          <t>Pro (1 месяц)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>25475</v>
+        <v>22183</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5414735</t>
+          <t>https://plati.market/itm/4881173</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sneelipo_615</t>
+          <t>Exclusive_Play</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ChatGPT PRO x20 1 месяц</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>25983</v>
+        <v>25475</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5696109</t>
+          <t>https://plati.market/itm/5414735</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OnePayNow</t>
+          <t>Sneelipo_615</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 1 месяц</t>
+          <t>ChatGPT PRO x20 1 месяц</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>26951</v>
+        <v>25983</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5290688</t>
+          <t>https://plati.market/itm/5696109</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pro Digital Goods</t>
+          <t>OnePayNow</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1 месяц ChatGPT PRO</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT Pro 1 месяц</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>14</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>28063</v>
+        <v>26951</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5777882</t>
+          <t>https://plati.market/itm/5290688</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>vvlstl</t>
+          <t>Pro Digital Goods</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pro (месяц)</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
+          <t>1 месяц ChatGPT PRO</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>29405</v>
+        <v>28063</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>https://plati.market/itm/5777882</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>vvlstl</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pro (месяц)</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>29405</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
           <t>https://plati.market/itm/4796860</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>SjMarket</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>1 месяц PRO</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D93" t="n">
         <v>12</v>
       </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3" t="n">
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
         <v>34990</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F92"/>
+  <autoFilter ref="A1:F93"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -6423,6 +6449,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/chatgpt_tariffs.xlsx
+++ b/docs/chatgpt_tariffs.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ChatGPT Plus" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ChatGPT Pro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT Plus" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT Pro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ChatGPT Plus'!$A$1:$F$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ChatGPT Pro'!$A$1:$F$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ChatGPT Plus'!$A$1:$F$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ChatGPT Pro'!$A$1:$F$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>26654</v>
+        <v>26655</v>
       </c>
       <c r="E45" t="n">
         <v>152</v>
@@ -1996,21 +1996,21 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5577477</t>
+          <t>https://plati.market/itm/5849306</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>accountstore4u</t>
+          <t>JensenLoantos</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chatgpt plus 1 months</t>
+          <t>ChatGPT Plus на 1 месяц без входа в систему</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>518</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2022,73 +2022,75 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5849306</t>
+          <t>https://plati.market/itm/5995043</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JensenLoantos</t>
+          <t>ImSubscribed</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ChatGPT Plus на 1 месяц без входа в систему</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
+          <t>ChatGPT Plus 1 месяц</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>2186</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5995043</t>
+          <t>https://plati.market/itm/5651002</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ImSubscribed</t>
+          <t>starfast</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ChatGPT Plus 1 месяц</t>
+          <t>ChatGPT Plus - на 1 месяц</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>2190</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5651002</t>
+          <t>https://plati.market/itm/4426502</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>starfast</t>
+          <t>ngthgila</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ChatGPT Plus - на 1 месяц</t>
+          <t>ChatGPT Plus – 1 месяц</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2097,26 +2099,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2199</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4426502</t>
+          <t>https://plati.market/itm/3218237</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ngthgila</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ChatGPT Plus – 1 месяц</t>
+          <t>PLUS 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2125,7 +2127,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>2215</v>
@@ -2134,205 +2136,205 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3218237</t>
+          <t>https://plati.market/itm/5559857</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>AltSubs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PLUS 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT Plus - 1 месяц: Обновление / Продление (Требуется Вход)</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>2215</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5559857</t>
+          <t>https://plati.market/itm/5763830</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AltSubs</t>
+          <t>PickBest</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ChatGPT Plus - 1 месяц: Обновление / Продление (Требуется Вход)</t>
+          <t>Chat GPT Plus  | 1 Month | On your Account | Ready Account</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>2234</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5763830</t>
+          <t>https://plati.market/itm/3804893</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PickBest</t>
+          <t>_RenS_</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chat GPT Plus  | 1 Month | On your Account | Ready Account</t>
+          <t>Plus - 1 месяц</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>2235</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3804893</t>
+          <t>https://plati.market/itm/5854702</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>_RenS_</t>
+          <t>SubVault</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plus - 1 месяц</t>
+          <t>TEAM BUSINESS PLUS ACCESS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>2255</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5854702</t>
+          <t>https://plati.market/itm/5873793</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SubVault</t>
+          <t>88Store AI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TEAM BUSINESS PLUS ACCESS</t>
+          <t>PLUS - 1 MONTH</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2260</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5873793</t>
+          <t>https://plati.market/itm/6021924</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>88Store AI</t>
+          <t>VEYRO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PLUS - 1 MONTH</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>6</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
+          <t>АКТИВАЦИЯ ChatGPT Plus — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>2285</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6021924</t>
+          <t>https://plati.market/itm/4481462</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VEYRO</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ ChatGPT Plus — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+          <t>АВТО 24/7 - [ChatGPT PLUS] - купить/продлить на ваш аккаунт - 1 мес - по ID аккаунта (без входа)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>2290</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4481462</t>
+          <t>https://plati.market/itm/3964931</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>AI GUO GUO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>АВТО 24/7 - [ChatGPT PLUS] - купить/продлить на ваш аккаунт - 1 мес - по ID аккаунта (без входа)</t>
+          <t>ChatGPT-Plus(1 МЕСЯЦ)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2344,32 +2346,34 @@
         <v>2</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>2299</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3964931</t>
+          <t>https://plati.market/itm/5424895</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AI GUO GUO</t>
+          <t>AppStops</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ChatGPT-Plus(1 МЕСЯЦ)</t>
+          <t>Plus подписка на месяц</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>2</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F70" s="3" t="n">
         <v>2300</v>
@@ -2378,127 +2382,123 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5424895</t>
+          <t>https://plati.market/itm/5865073</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AppStops</t>
+          <t>Genixai</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plus подписка на месяц</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>1: Активация/Продление ChatGPT Plus + Codex | Платная подписка на ваш Email | Без риска бана</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>9</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2300</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5865073</t>
+          <t>https://plati.market/itm/3235033</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Genixai</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1: Активация/Продление ChatGPT Plus + Codex | Платная подписка на ваш Email | Без риска бана</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>9</v>
+          <t>Активация/Продление ChatGPT Plus 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>2321</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3235033</t>
+          <t>https://plati.market/itm/4881173</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>Exclusive_Play</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Plus 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Plus</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>33</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>2326</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4881173</t>
+          <t>https://plati.market/itm/5800491</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Exclusive_Play</t>
+          <t>MaiDukAnh</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>[PLUS] Покупка / продление подписки на вашем аккаунте</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>2363</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5800491</t>
+          <t>https://plati.market/itm/5980351</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MaiDukAnh</t>
+          <t>IGROKLAD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[PLUS] Покупка / продление подписки на вашем аккаунте</t>
+          <t>ChatGPT PLUS [ НА 1 МЕСЯЦ ]</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -2508,153 +2508,155 @@
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>2381</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5980351</t>
+          <t>https://plati.market/itm/5657349</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IGROKLAD</t>
+          <t>RandowGMM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ChatGPT PLUS [ НА 1 МЕСЯЦ ]</t>
+          <t>1 месяц - ChatGPT Plus - на вашу учётную запись</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2383</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5657349</t>
+          <t>https://plati.market/itm/5960360</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RandowGMM</t>
+          <t>Subverse</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1 месяц - ChatGPT Plus - на вашу учётную запись</t>
+          <t>ChatGPT Plus • Поддержка Codex • Без подтверждения номера телефона • 100% Личный аккаунт (1 месяц)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5960360</t>
+          <t>https://plati.market/itm/5971718</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Subverse</t>
+          <t>Eleanning</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ChatGPT Plus • Поддержка Codex • Без подтверждения номера телефона • 100% Личный аккаунт (1 месяц)</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>2391</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5971718</t>
+          <t>https://plati.market/itm/4749723</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Eleanning</t>
+          <t>The Game Hub</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>Chat GPT Plus 1 месяц</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>2395</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4749723</t>
+          <t>https://plati.market/itm/4724944</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Game Hub</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chat GPT Plus 1 месяц</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>3</v>
+          <t>Апгрейд/Продление: ChatGPT Plus - 1 Месяц (Требуется Вход)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2400</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4724944</t>
+          <t>https://plati.market/itm/3931351</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>furfur</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Апгрейд/Продление: ChatGPT Plus - 1 Месяц (Требуется Вход)</t>
+          <t>ChatGPT PLUS 1 месяц</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2663,26 +2665,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>2407</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3931351</t>
+          <t>https://plati.market/itm/4880685</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>furfur</t>
+          <t>Cao Cacao</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ChatGPT PLUS 1 месяц</t>
+          <t>(1 МЕСЯЦ PLUS) Купите/Обновите подписку на своем аккаунте</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2691,171 +2693,171 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>2414</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4880685</t>
+          <t>https://plati.market/itm/6063473</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cao Cacao</t>
+          <t>of_existence</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>(1 МЕСЯЦ PLUS) Купите/Обновите подписку на своем аккаунте</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Plus — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>2427</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6063473</t>
+          <t>https://plati.market/itm/4873167</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>of_existence</t>
+          <t>digily</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Plus — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>0</v>
+          <t>ChatGPT Plus продление / активация на 1 месяц (на ваш аккаунт)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2437</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4873167</t>
+          <t>https://plati.market/itm/5981988</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>digily</t>
+          <t>HunterGPT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ChatGPT Plus продление / активация на 1 месяц (на ваш аккаунт)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Активация / Продление ChatGPT Plus — 1 МЕСЯЦ (Без входа в аккаунт | 24/7)</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>2438</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5981988</t>
+          <t>https://plati.market/itm/4695121</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HunterGPT</t>
+          <t>DigiSelling</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Активация / Продление ChatGPT Plus — 1 МЕСЯЦ (Без входа в аккаунт | 24/7)</t>
+          <t>Подписка PLUS 1 месяц</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2455</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4695121</t>
+          <t>https://plati.market/itm/4616358</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DigiSelling</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Подписка PLUS 1 месяц</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>61</v>
-      </c>
-      <c r="E87" t="n">
-        <v>2</v>
+          <t>[ChatGPT PLUS] готовый аккаунт с подпиской + почта на 1 месяц</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>2490</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4616358</t>
+          <t>https://plati.market/itm/4183350</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>SOFT_OPTOM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[ChatGPT PLUS] готовый аккаунт с подпиской + почта на 1 месяц</t>
+          <t>CHATGPT Plus 1 месяц БЫСТРО</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
         <v>2499</v>
@@ -2864,17 +2866,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4183350</t>
+          <t>https://plati.market/itm/5290688</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SOFT_OPTOM</t>
+          <t>Pro Digital Goods</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CHATGPT Plus 1 месяц БЫСТРО</t>
+          <t>1 месяц ChatGPT PLUS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2883,430 +2885,428 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>2499</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5290688</t>
+          <t>https://plati.market/itm/6009683</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pro Digital Goods</t>
+          <t>hakivana</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1 месяц ChatGPT PLUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Подписка Plus 1М - активация кодом</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>2508</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6009683</t>
+          <t>https://plati.market/itm/5465686</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>hakivana</t>
+          <t>DerdoArt</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Подписка Plus 1М - активация кодом</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>2511</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5465686</t>
+          <t>https://plati.market/itm/5998486</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DerdoArt</t>
+          <t>VantaStore</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plus</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>54</v>
-      </c>
-      <c r="E92" t="n">
-        <v>10</v>
+          <t>ChatGPT Plus - 1 месяц</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>2522</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5998486</t>
+          <t>https://plati.market/itm/4125885</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VantaStore</t>
+          <t>Будни Дизайнера</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ChatGPT Plus - 1 месяц</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>3</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>2550</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4125885</t>
+          <t>https://plati.market/itm/6002926</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Будни Дизайнера</t>
+          <t>Harvey Store</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Plus</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>2. ChatGPT PLUS - 1 месяц | В ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>2590</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6002926</t>
+          <t>https://plati.market/itm/5931604</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Harvey Store</t>
+          <t>MrKronos</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2. ChatGPT PLUS - 1 месяц | В ВАШ АККАУНТ</t>
+          <t>ChatGPT Plus</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>2598</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5931604</t>
+          <t>https://plati.market/itm/5974404</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MrKronos</t>
+          <t>Alexey Alexey</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ChatGPT Plus</t>
+          <t>ChatGPT Plus на 1 месяц | Активация и продление | На ваш аккаунт | Быстро | 24/7</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2612</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5974404</t>
+          <t>https://plati.market/itm/5877715</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alexey Alexey</t>
+          <t>DanyCyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ChatGPT Plus на 1 месяц | Активация и продление | На ваш аккаунт | Быстро | 24/7</t>
+          <t>ChatGPT Plus 1 месяц для новых пользователей</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>2617</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5877715</t>
+          <t>https://plati.market/itm/4591665</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DanyCyber</t>
+          <t>FoxyPayGlobal</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ChatGPT Plus 1 месяц для новых пользователей</t>
+          <t>Plus | Месяц | 1 участник</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>2697</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4591665</t>
+          <t>https://plati.market/itm/5654166</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FoxyPayGlobal</t>
+          <t>Easy_Pay</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Plus | Месяц | 1 участник</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>13</v>
+          <t>GPT PLUS 1 месяц на ваш аккаунт</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>&gt;10</t>
+        </is>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>2699</v>
+        <v>2778</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5654166</t>
+          <t>https://plati.market/itm/5688276</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Easy_Pay</t>
+          <t>Lyutsik_Shop</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GPT PLUS 1 месяц на ваш аккаунт</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>&gt;10</t>
-        </is>
+          <t>CHATGPT 5.2 PLUS  1 месяц по входу любой акк/ продление</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>79</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>2778</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5688276</t>
+          <t>https://plati.market/itm/5884270</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lyutsik_Shop</t>
+          <t>ProSeller.inc</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CHATGPT 5.2 PLUS  1 месяц по входу любой акк/ продление</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>79</v>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
+          <t>1. [АВТО 24/7] PLUS (1 месяц)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>2781</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5884270</t>
+          <t>https://plati.market/itm/5990295</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ProSeller.inc</t>
+          <t>PROMARKET88</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>1. [АВТО 24/7] PLUS (1 месяц)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>GPT PLUS</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>2799</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5990295</t>
+          <t>https://plati.market/itm/5700272</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PROMARKET88</t>
+          <t>OnePayNow</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GPT PLUS</t>
+          <t>ChatGPT Plus (используйте свой адрес электронной почты) - 1 месяц</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>2822</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5700272</t>
+          <t>https://plati.market/itm/5144685</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OnePayNow</t>
+          <t>D.O.G.E. PRIME SHOP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ChatGPT Plus (используйте свой адрес электронной почты) - 1 месяц</t>
+          <t>Plus (1 месяц)</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>2825</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5144685</t>
+          <t>https://plati.market/itm/6039145</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>D.O.G.E. PRIME SHOP</t>
+          <t>Podpiska_pro_shop</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Plus (1 месяц)</t>
+          <t>Ключ продления вашего аккаунта · без активной Plus</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -3316,259 +3316,259 @@
         <v>0</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>2845</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6039145</t>
+          <t>https://plati.market/itm/5627185</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Podpiska_pro_shop</t>
+          <t>cheapyet</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ключ продления вашего аккаунта · без активной Plus</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>0</v>
+          <t>ChatGPT Plus — 1 месяц бесплатно (премиум-версия, полный доступ к функциям)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>2883</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5627185</t>
+          <t>https://plati.market/itm/5777882</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>cheapyet</t>
+          <t>vvlstl</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ChatGPT Plus — 1 месяц бесплатно (премиум-версия, полный доступ к функциям)</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Plus (месяц)</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>2910</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5777882</t>
+          <t>https://plati.market/itm/3919475</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>vvlstl</t>
+          <t>Schiphol Shopping</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Plus (месяц)</t>
+          <t>ChatGPT 4 Plus (GPT-4 Turbo) + DALL·E: 1 месяц</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>2941</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3919475</t>
+          <t>https://plati.market/itm/5768610</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Schiphol Shopping</t>
+          <t>Beast Seller</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ChatGPT 4 Plus (GPT-4 Turbo) + DALL·E: 1 месяц</t>
+          <t>ChatGPT Plus (1 Month)</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>2957</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5768610</t>
+          <t>https://plati.market/itm/5087858</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Beast Seller</t>
+          <t>FUNFINITY SHOP</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ChatGPT Plus (1 Month)</t>
+          <t>Plus 1 Месяц</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>2974</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5087858</t>
+          <t>https://plati.market/itm/4796860</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FUNFINITY SHOP</t>
+          <t>SjMarket</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Plus 1 Месяц</t>
+          <t>1 месяц PLUS</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>2985</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4796860</t>
+          <t>https://plati.market/itm/4828424</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SjMarket</t>
+          <t>Schiphol Shopping</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1 месяц PLUS</t>
+          <t>ChatGPT 4 Plus (GPT-4 Turbo) + DALL·E: 1 месяц</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>2990</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4828424</t>
+          <t>https://plati.market/itm/5897564</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Schiphol Shopping</t>
+          <t>Ai_Box</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ChatGPT 4 Plus (GPT-4 Turbo) + DALL·E: 1 месяц</t>
+          <t>Plus 1 Месяц [ ХИТ ]</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>3081</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5897564</t>
+          <t>https://plati.market/itm/5870331</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ai_Box</t>
+          <t>karlincards</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Plus 1 Месяц [ ХИТ ]</t>
+          <t>НОВАЯ учетная запись ChatGPT PLUS 1 МЕСЯЦ — доставка вручную / полный доступ включен</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>3168</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5870331</t>
+          <t>https://plati.market/itm/5808730</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>karlincards</t>
+          <t>wall058</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>НОВАЯ учетная запись ChatGPT PLUS 1 МЕСЯЦ — доставка вручную / полный доступ включен</t>
+          <t>1 Month Chatgpt PLUS</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -3578,89 +3578,63 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>3260</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5808730</t>
+          <t>https://plati.market/itm/5438178</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>wall058</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>1 Month Chatgpt PLUS</t>
+          <t>ChatGPT Plus Аккаунт - 12 Месяцев (Случайный Email) [САМОЕ БЫСТРОЕ, ДЕШЕВЛЕ ВСЕХ!]</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>3441</v>
+        <v>25700</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5438178</t>
+          <t>https://plati.market/itm/5429452</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>QuickSales</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ChatGPT Plus Аккаунт - 12 Месяцев (Случайный Email) [САМОЕ БЫСТРОЕ, ДЕШЕВЛЕ ВСЕХ!]</t>
+          <t>24/7 | ChatGPT 5 PLUS</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>25700</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>https://plati.market/itm/5429452</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>QuickSales</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>24/7 | ChatGPT 5 PLUS</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>9</v>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="3" t="n">
         <v>35268</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F118"/>
+  <autoFilter ref="A1:F117"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -3778,7 +3752,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3790,7 +3763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -3836,69 +3809,71 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5422669</t>
+          <t>https://plati.market/itm/4125885</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SpicyCheeze</t>
+          <t>Будни Дизайнера</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1 - Месяц | PRO | Без Gemini</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>467</v>
+          <t>PRO X5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>170</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5979732</t>
+          <t>https://plati.market/itm/6031453</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LevelX DZ</t>
+          <t>SiberAI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 1 месяц – Совместный аккаунт | Безопасный и надёжный доступ</t>
+          <t>Активация/Продление ChatGPT Pro 5X 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1104</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4125885</t>
+          <t>https://plati.market/itm/5143806</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Будни Дизайнера</t>
+          <t>CorzySell</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PRO X5</t>
+          <t>Pro x5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3907,52 +3882,54 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>8590</v>
+        <v>9099</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6031453</t>
+          <t>https://plati.market/itm/5912754</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SiberAI</t>
+          <t>SiberiaPlay</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 5X 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>59</v>
+          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9000</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5143806</t>
+          <t>https://plati.market/itm/5636225</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CorzySell</t>
+          <t>NNStore</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pro x5</t>
+          <t>Chat GPT PRO x5 | CODEX - Готовый аккаунт</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3961,26 +3938,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>9099</v>
+        <v>9331</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5912754</t>
+          <t>https://plati.market/itm/5734457</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SiberiaPlay</t>
+          <t>KABAN STORE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
+          <t>3. [АКЦИЯ] ChatGPT Pro X5 1 МЕСЯЦ l Подписка / Продление (на Ваш аккаунт, без входа, за минуту)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3989,26 +3966,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>9300</v>
+        <v>9379</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5636225</t>
+          <t>https://plati.market/itm/5896950</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NNStore</t>
+          <t>SiberiaPlay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chat GPT PRO x5 | CODEX - Готовый аккаунт</t>
+          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4020,23 +3997,23 @@
         <v>2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>9331</v>
+        <v>9388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5734457</t>
+          <t>https://plati.market/itm/5785342</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KABAN STORE</t>
+          <t>Geniya</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3. [АКЦИЯ] ChatGPT Pro X5 1 МЕСЯЦ l Подписка / Продление (на Ваш аккаунт, без входа, за минуту)</t>
+          <t>24/7 АВТО | Chat gpt PRO Х5 1 МЕСЯЦ Активация/продление (На ваш аккаунт без входа за минуту)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4045,182 +4022,182 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9379</v>
+        <v>9399</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5896950</t>
+          <t>https://plati.market/itm/6041416</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SiberiaPlay</t>
+          <t>PAYFLIX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
+          <t>[24/7 АВТОВЫДАЧА] Chat GPT PRO 5X | АКТИВАЦИЯ / ПРОДЛЕНИЕ | 1 МЕСЯЦ | БЕЗ ВХОДА | ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9388</v>
+        <v>9499</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5785342</t>
+          <t>https://plati.market/itm/3521831</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Geniya</t>
+          <t>tahonya</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>24/7 АВТО | Chat gpt PRO Х5 1 МЕСЯЦ Активация/продление (На ваш аккаунт без входа за минуту)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>PRO X5 НА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9399</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6041416</t>
+          <t>https://plati.market/itm/5218986</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PAYFLIX</t>
+          <t>northernlights</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[24/7 АВТОВЫДАЧА] Chat GPT PRO 5X | АКТИВАЦИЯ / ПРОДЛЕНИЕ | 1 МЕСЯЦ | БЕЗ ВХОДА | ВАШ АККАУНТ</t>
+          <t>ChatGPT Pro 5x</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;50</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>9499</v>
+        <v>9633</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3521831</t>
+          <t>https://plati.market/itm/5856306</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tahonya</t>
+          <t>GameLootGG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PRO X5 НА МЕСЯЦ</t>
+          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 - 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>9600</v>
+        <v>9638</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5218986</t>
+          <t>https://plati.market/itm/6051702</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>northernlights</t>
+          <t>KappaStore</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5x</t>
+          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>&gt;50</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>9633</v>
+        <v>9839</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5856306</t>
+          <t>https://plati.market/itm/4306654</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GameLootGG</t>
+          <t>fursov.me</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 - 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>65</v>
+          <t>3. Продление ChatGPT PRO X5 — 1 МЕСЯЦ | На Ваш аккаунт | Оф.Метод</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>9638</v>
+        <v>9949</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6051702</t>
+          <t>https://plati.market/itm/5834250</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4239,170 +4216,170 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9839</v>
+        <v>9969</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4306654</t>
+          <t>https://plati.market/itm/5995043</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fursov.me</t>
+          <t>ImSubscribed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3. Продление ChatGPT PRO X5 — 1 МЕСЯЦ | На Ваш аккаунт | Оф.Метод</t>
+          <t>ChatGPT Pro x5 1 месяц</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>98</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>9949</v>
+        <v>9989</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5834250</t>
+          <t>https://plati.market/itm/4695121</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KappaStore</t>
+          <t>DigiSelling</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Подписка PRO x5  1 месяц</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>61</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9969</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5995043</t>
+          <t>https://plati.market/itm/5162565</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ImSubscribed</t>
+          <t>DigiSelling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ChatGPT Pro x5 1 месяц</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>Оформление подписки PRO на ваш аккаунт</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>9989</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4695121</t>
+          <t>https://plati.market/itm/5352918</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DigiSelling</t>
+          <t>forYou97</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Подписка PRO x5  1 месяц</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>61</v>
+          <t>2. Активация/Продление ChatGPT Pro x5 1 МЕСЯЦ (на ваш аккаунт, быстро, без входа))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>9990</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5162565</t>
+          <t>https://plati.market/itm/4339002</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DigiSelling</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Оформление подписки PRO на ваш аккаунт</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
+          <t>7. [Скидка] ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>9990</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5352918</t>
+          <t>https://plati.market/itm/5407372</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>forYou97</t>
+          <t>STORE_IZI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2. Активация/Продление ChatGPT Pro x5 1 МЕСЯЦ (на ваш аккаунт, быстро, без входа))</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4414,17 +4391,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4339002</t>
+          <t>https://plati.market/itm/3218237</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7. [Скидка] ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+          <t>PRO X5 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4432,55 +4409,55 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+      <c r="E23" t="n">
+        <v>28</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>9999</v>
+        <v>10064</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5407372</t>
+          <t>https://plati.market/itm/3235033</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STORE_IZI</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>21</v>
+          <t>Активация/Продление ChatGPT PRO X5 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>9999</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3218237</t>
+          <t>https://plati.market/itm/4371645</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>MyKEYS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PRO X5 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
+          <t>ChatGPT PRO 5x - 1 месяц (5.6)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4489,54 +4466,56 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10064</v>
+        <v>10199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3235033</t>
+          <t>https://plati.market/itm/5992061</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>Kernel_JX</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT PRO X5 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
+          <t>[АВТО 24/7 ] ChatGPT PRO 5X 1 месяц | АКТИВАЦИЯ / ПРОДЛЕНИЕ ( без логина, на ваш аккаунт)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>10078</v>
+        <v>10273</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4371645</t>
+          <t>https://plati.market/itm/3725372</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MyKEYS</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x - 1 месяц (5.6)</t>
+          <t>АВТО 24/7| Активация/ Продление CHATGPT PRO X5 на 1 месяц (Ваш аккаунт, без логина) ГАРАНТИЯ 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4545,26 +4524,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10199</v>
+        <v>10401</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5992061</t>
+          <t>https://plati.market/itm/6021924</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kernel_JX</t>
+          <t>VEYRO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[АВТО 24/7 ] ChatGPT PRO 5X 1 месяц | АКТИВАЦИЯ / ПРОДЛЕНИЕ ( без логина, на ваш аккаунт)</t>
+          <t>АКТИВАЦИЯ ChatGPT Pro X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4578,23 +4557,23 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>10273</v>
+        <v>10499</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3725372</t>
+          <t>https://plati.market/itm/4802730</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>northernlights</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>АВТО 24/7| Активация/ Продление CHATGPT PRO X5 на 1 месяц (Ваш аккаунт, без логина) ГАРАНТИЯ 1 МЕСЯЦ</t>
+          <t>Подписка ChatGPT Pro 5x</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4603,56 +4582,54 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10401</v>
+        <v>10591</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6021924</t>
+          <t>https://plati.market/itm/4380086</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VEYRO</t>
+          <t>MyKEYS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ ChatGPT Pro X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+          <t>ChatGPT PRO 5x - 1 месяц (5.5)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>10499</v>
+        <v>10599</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4802730</t>
+          <t>https://plati.market/itm/3705934</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>northernlights</t>
+          <t>hayta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Подписка ChatGPT Pro 5x</t>
+          <t>3. 24/7 АВТО | ChatGPT PRO X5 1 МЕСЯЦ | Подписка (на Ваш аккаунт, без входа, за минуту)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4661,26 +4638,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10591</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4380086</t>
+          <t>https://plati.market/itm/5794510</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MyKEYS</t>
+          <t>BuyForGame</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x - 1 месяц (5.5)</t>
+          <t>[БЕЗ ВХОДА] АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | ЗА МИНУТУ | НА ВАШ АККАУНТ |</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4689,54 +4666,56 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>10599</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3705934</t>
+          <t>https://plati.market/itm/5214484</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>hayta</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3. 24/7 АВТО | ChatGPT PRO X5 1 МЕСЯЦ | Подписка (на Ваш аккаунт, без входа, за минуту)</t>
+          <t>[ChatGPT PRO 5x] на 1 месяц – активация на ваш аккаунт (с передачей логина и пароля, со входом)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>7</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>10735</v>
+        <v>10999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5794510</t>
+          <t>https://plati.market/itm/4313142</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BuyForGame</t>
+          <t>ProSeller.inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>[БЕЗ ВХОДА] АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | ЗА МИНУТУ | НА ВАШ АККАУНТ |</t>
+          <t>2. PRO 5x (1 месяц)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4745,16 +4724,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>10899</v>
+        <v>10999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5214484</t>
+          <t>https://plati.market/itm/4481462</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4764,37 +4743,35 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] на 1 месяц – активация на ваш аккаунт (с передачей логина и пароля, со входом)</t>
+          <t>[ChatGPT PRO 5x] - купить/продлить на ваш аккаунт - 1 мес - со входом (логин+пароль) [РУЧНАЯ]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>10999</v>
+        <v>11199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4313142</t>
+          <t>https://plati.market/itm/5807701</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ProSeller.inc</t>
+          <t>Mahoraga borz</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2. PRO 5x (1 месяц)</t>
+          <t>Продление \ ChatGPT Pro x5 на 1 месяц (на ваш аккаунт, без входа в аккаунт)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4803,54 +4780,52 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>10999</v>
+        <v>11205</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4481462</t>
+          <t>https://plati.market/itm/5980351</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>IGROKLAD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] - купить/продлить на ваш аккаунт - 1 мес - со входом (логин+пароль) [РУЧНАЯ]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT PRO [ НА 1 МЕСЯЦ ]</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>11199</v>
+        <v>11345</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5807701</t>
+          <t>https://plati.market/itm/3859725</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mahoraga borz</t>
+          <t>fursov.me</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Продление \ ChatGPT Pro x5 на 1 месяц (на ваш аккаунт, без входа в аккаунт)</t>
+          <t>GPT PRO X5 &gt;&gt; Новый аккаунт + Почта (1 месяц)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4859,52 +4834,56 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>11205</v>
+        <v>11349</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5980351</t>
+          <t>https://plati.market/itm/6063721</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IGROKLAD</t>
+          <t>MORPHEUSINTELLIGENCE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ChatGPT PRO [ НА 1 МЕСЯЦ ]</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
+          <t>ChatGPT Pro 5X</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>11345</v>
+        <v>11390</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3859725</t>
+          <t>https://plati.market/itm/3648532</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fursov.me</t>
+          <t>UgolokH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GPT PRO X5 &gt;&gt; Новый аккаунт + Почта (1 месяц)</t>
+          <t>PRO X5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4913,200 +4892,200 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>11349</v>
+        <v>11490</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6063721</t>
+          <t>https://plati.market/itm/5481303</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MORPHEUSINTELLIGENCE</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5X</t>
+          <t>ChatGPT PRO X5 1 месяц (код активации)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>11390</v>
+        <v>11749</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3648532</t>
+          <t>https://plati.market/itm/5424895</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UgolokH</t>
+          <t>AppStops</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PRO X5</t>
+          <t>Pro подписка на месяц</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>11490</v>
+        <v>11790</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5481303</t>
+          <t>https://plati.market/itm/6055394</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>MisterHeisenberg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 1 месяц (код активации)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Активация/Продление ChatGPT PRO x5 1 МЕСЯЦ на ваш аккаунт</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>11749</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5424895</t>
+          <t>https://plati.market/itm/4339392</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AppStops</t>
+          <t>MARCEL VPN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pro подписка на месяц</t>
+          <t>2.АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Pro X5 — 1 МЕСЯЦ |  НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>11790</v>
+        <v>11889</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6055394</t>
+          <t>https://plati.market/itm/4756087</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MisterHeisenberg</t>
+          <t>IronMarvell</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT PRO x5 1 МЕСЯЦ на ваш аккаунт</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
+          <t>ChatGPT PRO 5x 1 месяц</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>11800</v>
+        <v>11990</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4339392</t>
+          <t>https://plati.market/itm/4616358</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MARCEL VPN</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2.АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Pro X5 — 1 МЕСЯЦ |  НА ВАШ АККАУНТ</t>
+          <t>[ChatGPT PRO 5x] готовый аккаунт с подпиской + почта на 1 месяц</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>&gt;100</t>
+          <t>скрыто</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>&gt;100</t>
+          <t>скрыто</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>11889</v>
+        <v>11999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4756087</t>
+          <t>https://plati.market/itm/3931351</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IronMarvell</t>
+          <t>furfur</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x 1 месяц</t>
+          <t>ChatGPT PRO 1 месяц x5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5115,56 +5094,52 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>11990</v>
+        <v>12002</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4616358</t>
+          <t>https://plati.market/itm/6063473</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>of_existence</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] готовый аккаунт с подпиской + почта на 1 месяц</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11999</v>
+        <v>12068</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3931351</t>
+          <t>https://plati.market/itm/4853415</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>furfur</t>
+          <t>Super Man</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 1 месяц x5</t>
+          <t>ChatGPT PRO X5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5173,184 +5148,186 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12002</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6063473</t>
+          <t>https://plati.market/itm/5361993</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>of_existence</t>
+          <t>ZaruBot</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+          <t>ChatGPT PRO 5x 1 месяц {Для старых и новых (обеих) учетных записей {Продление}</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12068</v>
+        <v>12269</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4853415</t>
+          <t>https://plati.market/itm/5865073</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Super Man</t>
+          <t>Genixai</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>4: ChatGPT Pro 5X | Активация на ваш Email | Высокие лимиты | Полная гарантия</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>12100</v>
+        <v>12279</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5361993</t>
+          <t>https://plati.market/itm/5931604</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ZaruBot</t>
+          <t>MrKronos</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x 1 месяц {Для старых и новых (обеих) учетных записей {Продление}</t>
+          <t>ChatGPT PRO 5x</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>12269</v>
+        <v>12290</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5865073</t>
+          <t>https://plati.market/itm/5849306</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Genixai</t>
+          <t>JensenLoantos</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4: ChatGPT Pro 5X | Активация на ваш Email | Высокие лимиты | Полная гарантия</t>
+          <t>ChatGPT Pro на 1 месяц без входа в систему</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>12279</v>
+        <v>12318</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5931604</t>
+          <t>https://plati.market/itm/4362367</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MrKronos</t>
+          <t>AccountBroker</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
+          <t>3.Активация/Продление ChatGPT Pro 5x 1 МЕСЯЦ (Без входа с использованием файлов cookie)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>12290</v>
+        <v>12469</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5849306</t>
+          <t>https://plati.market/itm/5897564</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JensenLoantos</t>
+          <t>Ai_Box</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ChatGPT Pro на 1 месяц без входа в систему</t>
+          <t>Pro 5X [ ЛУЧШАЯ ЦЕНА ]</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>121</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>12318</v>
+        <v>12584</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4362367</t>
+          <t>https://plati.market/itm/3683609</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AccountBroker</t>
+          <t>_RenS_</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.Активация/Продление ChatGPT Pro 5x 1 МЕСЯЦ (Без входа с использованием файлов cookie)</t>
+          <t>У меня уже есть аккаунт ChatGPT (оформляется подписка Pro без входа в аккаунт)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5358,233 +5335,231 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+      <c r="E56" t="n">
+        <v>5</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>12469</v>
+        <v>12609</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5897564</t>
+          <t>https://plati.market/itm/6057697</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ai_Box</t>
+          <t>SubVault</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pro 5X [ ЛУЧШАЯ ЦЕНА ]</t>
+          <t>Activation/Renewal ChatGPT Pro 5X – 1 месяц | Высокие лимиты | На ваш Email | Требуется вход</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>12584</v>
+        <v>12640</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3683609</t>
+          <t>https://plati.market/itm/5960360</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>_RenS_</t>
+          <t>Subverse</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>У меня уже есть аккаунт ChatGPT (оформляется подписка Pro без входа в аккаунт)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT Pro 5x • Официальный доступ • Полная гарантия</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>12609</v>
+        <v>12651</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6057697</t>
+          <t>https://plati.market/itm/5873793</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SubVault</t>
+          <t>88Store AI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Activation/Renewal ChatGPT Pro 5X – 1 месяц | Высокие лимиты | На ваш Email | Требуется вход</t>
+          <t>PRO x5 - 1 MONTH</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>12640</v>
+        <v>12717</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5960360</t>
+          <t>https://plati.market/itm/5763830</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Subverse</t>
+          <t>PickBest</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5x • Официальный доступ • Полная гарантия</t>
+          <t>Chat GPT  Pro 5x | 1 Month | On your Account | Ready Account</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>12651</v>
+        <v>13119</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5873793</t>
+          <t>https://plati.market/itm/6052016</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>88Store AI</t>
+          <t>DigiMari</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PRO x5 - 1 MONTH</t>
+          <t>Активация / Продление ChatGPT PRO - 1 МЕС | ВАШ Аккаунт</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>12717</v>
+        <v>13153</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5763830</t>
+          <t>https://plati.market/itm/5998486</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PickBest</t>
+          <t>VantaStore</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chat GPT  Pro 5x | 1 Month | On your Account | Ready Account</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>6</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
+          <t>ChatGPT Pro x5 - 1 месяц</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>13119</v>
+        <v>13277</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6052016</t>
+          <t>https://plati.market/itm/3964931</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DigiMari</t>
+          <t>AI GUO GUO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Активация / Продление ChatGPT PRO - 1 МЕС | ВАШ Аккаунт</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
+          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>13153</v>
+        <v>13340</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5998486</t>
+          <t>https://plati.market/itm/5990295</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VantaStore</t>
+          <t>PROMARKET88</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ChatGPT Pro x5 - 1 месяц</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>GPT PRO</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>13277</v>
+        <v>13402</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3964931</t>
+          <t>https://plati.market/itm/5869102</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5597,242 +5572,244 @@
           <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+      <c r="D65" t="n">
+        <v>212</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>13340</v>
+        <v>13512</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5990295</t>
+          <t>https://plati.market/itm/4724944</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PROMARKET88</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GPT PRO</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>2</v>
+          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Без Входа)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>13402</v>
+        <v>13667</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5869102</t>
+          <t>https://plati.market/itm/5465686</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AI GUO GUO</t>
+          <t>DerdoArt</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+          <t>Pro x5</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>212</v>
+        <v>54</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>13512</v>
+        <v>14159</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4724944</t>
+          <t>https://plati.market/itm/5688276</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>Lyutsik_Shop</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Без Входа)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>CHATGPT 5.2 PRO 1 месяц ПОДПИСКА С ЗАХОДОМ НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>79</v>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>13667</v>
+        <v>14229</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5465686</t>
+          <t>https://plati.market/itm/5981988</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>DerdoArt</t>
+          <t>HunterGPT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pro x5</t>
+          <t>Активация/Продление ChatGPT Pro 5X — 1 МЕСЯЦ (Требуется вход в аккаунт | 24/7)</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="E69" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>14159</v>
+        <v>14326</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5688276</t>
+          <t>https://plati.market/itm/6002830</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lyutsik_Shop</t>
+          <t>67_Shop</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CHATGPT 5.2 PRO 1 месяц ПОДПИСКА С ЗАХОДОМ НА ВАШ АККАУНТ</t>
+          <t>ChatGPT PRO 5X — 1 месяц | На ваш аккаунт | Без входа</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>14229</v>
+        <v>14981</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5981988</t>
+          <t>https://plati.market/itm/3636620</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HunterGPT</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 5X — 1 МЕСЯЦ (Требуется вход в аккаунт | 24/7)</t>
+          <t>4. ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13</v>
+        <v>26655</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>14326</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6002830</t>
+          <t>https://plati.market/itm/4183350</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>67_Shop</t>
+          <t>SOFT_OPTOM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5X — 1 месяц | На ваш аккаунт | Без входа</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>39</v>
+          <t>CHATGPT Pro 1 месяц БЫСТРО x5</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>14981</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3636620</t>
+          <t>https://plati.market/itm/5651002</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>starfast</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>4. ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>26654</v>
+          <t>ChatGPT Pro X5 - на 1 Месяц</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E73" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>14999</v>
+        <v>15399</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4183350</t>
+          <t>https://plati.market/itm/5401296</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SOFT_OPTOM</t>
+          <t>tuanbes</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CHATGPT Pro 1 месяц БЫСТРО x5</t>
+          <t>ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5841,289 +5818,287 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>14999</v>
+        <v>15434</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5651002</t>
+          <t>https://plati.market/itm/5884270</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>starfast</t>
+          <t>ProSeller.inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ChatGPT Pro X5 - на 1 Месяц</t>
+          <t>2. PRO 5x (1 месяц)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>15399</v>
+        <v>15799</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5401296</t>
+          <t>https://plati.market/itm/4591665</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>tuanbes</t>
+          <t>FoxyPayGlobal</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Pro | Месяц  | 1 участник</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13</v>
       </c>
       <c r="E76" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>15434</v>
+        <v>16049</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5884270</t>
+          <t>https://plati.market/itm/5877715</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ProSeller.inc</t>
+          <t>DanyCyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2. PRO 5x (1 месяц)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>Активация/продление подписки ChatGPT Pro 5 раз по 1 месяц</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>15799</v>
+        <v>16179</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4591665</t>
+          <t>https://plati.market/itm/5437983</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FoxyPayGlobal</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pro | Месяц  | 1 участник</t>
+          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Требуется Вход)</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>16049</v>
+        <v>16246</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5877715</t>
+          <t>https://plati.market/itm/5087858</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DanyCyber</t>
+          <t>FUNFINITY SHOP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Активация/продление подписки ChatGPT Pro 5 раз по 1 месяц</t>
+          <t>Pro 1 Месяц (x5)</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>16179</v>
+        <v>16516</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5437983</t>
+          <t>https://plati.market/itm/5870331</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>karlincards</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Требуется Вход)</t>
+          <t>НОВАЯ учетная запись ChatGPT PRO X5 1 МЕСЯЦ (новая учетная запись с доступом к электронной почте)</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>16246</v>
+        <v>19554</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5087858</t>
+          <t>https://plati.market/itm/5660318</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FUNFINITY SHOP</t>
+          <t>sashasale</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pro 1 Месяц (x5)</t>
+          <t>Активация/Продление ChatGPT Pro 20x 1 месяц (Без Входа)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>16516</v>
+        <v>19899</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5870331</t>
+          <t>https://plati.market/itm/5559857</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>karlincards</t>
+          <t>AltSubs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>НОВАЯ учетная запись ChatGPT PRO X5 1 МЕСЯЦ (новая учетная запись с доступом к электронной почте)</t>
+          <t>ChatGPT Pro - 1 месяц: новый аккаунт (полный доступ)</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>19554</v>
+        <v>21403</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5660318</t>
+          <t>https://plati.market/itm/5144685</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>sashasale</t>
+          <t>D.O.G.E. PRIME SHOP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 20x 1 месяц (Без Входа)</t>
+          <t>Pro (1 месяц)</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>19899</v>
+        <v>21809</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5559857</t>
+          <t>https://plati.market/itm/3714311</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AltSubs</t>
+          <t>Luxtake</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ChatGPT Pro - 1 месяц: новый аккаунт (полный доступ)</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10</v>
+          <t>3. 24/7 АВТО | Продление ChatGPT PRO — 1 МЕСЯЦ | На Ваш аккаунт | Без входа | За минуту</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>21403</v>
+        <v>21975</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5144685</t>
+          <t>https://plati.market/itm/5231895</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>D.O.G.E. PRIME SHOP</t>
+          <t>PREMIUMSTOREXYZ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6131,232 +6106,178 @@
           <t>Pro (1 месяц)</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>0</v>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>21809</v>
+        <v>22183</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3714311</t>
+          <t>https://plati.market/itm/4881173</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Luxtake</t>
+          <t>Exclusive_Play</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3. 24/7 АВТО | Продление ChatGPT PRO — 1 МЕСЯЦ | На Ваш аккаунт | Без входа | За минуту</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>33</v>
       </c>
       <c r="E86" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>21975</v>
+        <v>25475</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5231895</t>
+          <t>https://plati.market/itm/5414735</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PREMIUMSTOREXYZ</t>
+          <t>Sneelipo_615</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pro (1 месяц)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT PRO x20 1 месяц</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>7</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>22183</v>
+        <v>25983</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4881173</t>
+          <t>https://plati.market/itm/5696109</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Exclusive_Play</t>
+          <t>OnePayNow</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pro</t>
+          <t>ChatGPT Pro 1 месяц</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>25475</v>
+        <v>26951</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5414735</t>
+          <t>https://plati.market/itm/5290688</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sneelipo_615</t>
+          <t>Pro Digital Goods</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ChatGPT PRO x20 1 месяц</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>7</v>
+          <t>1 месяц ChatGPT PRO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>25983</v>
+        <v>28063</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5696109</t>
+          <t>https://plati.market/itm/5777882</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OnePayNow</t>
+          <t>vvlstl</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 1 месяц</t>
+          <t>Pro (месяц)</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>26951</v>
+        <v>29405</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5290688</t>
+          <t>https://plati.market/itm/4796860</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pro Digital Goods</t>
+          <t>SjMarket</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1 месяц ChatGPT PRO</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>1 месяц PRO</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12</v>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>28063</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>https://plati.market/itm/5777882</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>vvlstl</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Pro (месяц)</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>29405</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>https://plati.market/itm/4796860</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>SjMarket</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1 месяц PRO</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>12</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" s="3" t="n">
         <v>34990</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F93"/>
+  <autoFilter ref="A1:F91"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -6448,8 +6369,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/chatgpt_tariffs.xlsx
+++ b/docs/chatgpt_tariffs.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT Plus" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChatGPT Pro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ChatGPT Plus" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ChatGPT Pro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ChatGPT Plus'!$A$1:$F$117</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ChatGPT Pro'!$A$1:$F$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ChatGPT Pro'!$A$1:$F$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3763,7 +3763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="75" customWidth="1" min="1" max="1"/>
@@ -3809,99 +3809,97 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4125885</t>
+          <t>https://plati.market/itm/5422669</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Будни Дизайнера</t>
+          <t>SpicyCheeze</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PRO X5</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>1 - Месяц | PRO | Без Gemini</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>467</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>8590</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6031453</t>
+          <t>https://plati.market/itm/4125885</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SiberAI</t>
+          <t>Будни Дизайнера</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 5X 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>59</v>
+          <t>PRO X5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>9000</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5143806</t>
+          <t>https://plati.market/itm/6031453</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CorzySell</t>
+          <t>SiberAI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pro x5</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Активация/Продление ChatGPT Pro 5X 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>59</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>9099</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5912754</t>
+          <t>https://plati.market/itm/5143806</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SiberiaPlay</t>
+          <t>CorzySell</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
+          <t>Pro x5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3913,23 +3911,23 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>9300</v>
+        <v>9099</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5636225</t>
+          <t>https://plati.market/itm/5912754</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NNStore</t>
+          <t>SiberiaPlay</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chat GPT PRO x5 | CODEX - Готовый аккаунт</t>
+          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3938,26 +3936,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>9331</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5734457</t>
+          <t>https://plati.market/itm/5636225</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KABAN STORE</t>
+          <t>NNStore</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3. [АКЦИЯ] ChatGPT Pro X5 1 МЕСЯЦ l Подписка / Продление (на Ваш аккаунт, без входа, за минуту)</t>
+          <t>Chat GPT PRO x5 | CODEX - Готовый аккаунт</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3966,26 +3964,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>9379</v>
+        <v>9331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5896950</t>
+          <t>https://plati.market/itm/5734457</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SiberiaPlay</t>
+          <t>KABAN STORE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
+          <t>3. [АКЦИЯ] ChatGPT Pro X5 1 МЕСЯЦ l Подписка / Продление (на Ваш аккаунт, без входа, за минуту)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3994,26 +3992,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>9388</v>
+        <v>9379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5785342</t>
+          <t>https://plati.market/itm/5896950</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Geniya</t>
+          <t>SiberiaPlay</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>24/7 АВТО | Chat gpt PRO Х5 1 МЕСЯЦ Активация/продление (На ваш аккаунт без входа за минуту)</t>
+          <t>• [24/7 АВТОВЫДАЧА. Активация / продление] Подписка ChatGPT 5.6 Pro X5 - 1 месяц</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4025,161 +4023,161 @@
         <v>2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>9399</v>
+        <v>9388</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6041416</t>
+          <t>https://plati.market/itm/5785342</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PAYFLIX</t>
+          <t>Geniya</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[24/7 АВТОВЫДАЧА] Chat GPT PRO 5X | АКТИВАЦИЯ / ПРОДЛЕНИЕ | 1 МЕСЯЦ | БЕЗ ВХОДА | ВАШ АККАУНТ</t>
+          <t>24/7 АВТО | Chat gpt PRO Х5 1 МЕСЯЦ Активация/продление (На ваш аккаунт без входа за минуту)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9499</v>
+        <v>9399</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3521831</t>
+          <t>https://plati.market/itm/6041416</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>tahonya</t>
+          <t>PAYFLIX</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PRO X5 НА МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>69</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
+          <t>[24/7 АВТОВЫДАЧА] Chat GPT PRO 5X | АКТИВАЦИЯ / ПРОДЛЕНИЕ | 1 МЕСЯЦ | БЕЗ ВХОДА | ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>9600</v>
+        <v>9499</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5218986</t>
+          <t>https://plati.market/itm/3521831</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>northernlights</t>
+          <t>tahonya</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5x</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>&gt;50</t>
-        </is>
+          <t>PRO X5 НА МЕСЯЦ</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>9633</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5856306</t>
+          <t>https://plati.market/itm/5218986</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GameLootGG</t>
+          <t>northernlights</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 - 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>65</v>
+          <t>ChatGPT Pro 5x</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>&gt;50</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>9638</v>
+        <v>9633</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6051702</t>
+          <t>https://plati.market/itm/5856306</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KappaStore</t>
+          <t>GameLootGG</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 - 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>65</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>9839</v>
+        <v>9638</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4306654</t>
+          <t>https://plati.market/itm/6051702</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fursov.me</t>
+          <t>KappaStore</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3. Продление ChatGPT PRO X5 — 1 МЕСЯЦ | На Ваш аккаунт | Оф.Метод</t>
+          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4188,26 +4186,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>9949</v>
+        <v>9839</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5834250</t>
+          <t>https://plati.market/itm/4306654</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KappaStore</t>
+          <t>fursov.me</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
+          <t>3. Продление ChatGPT PRO X5 — 1 МЕСЯЦ | На Ваш аккаунт | Оф.Метод</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4216,72 +4214,74 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>9969</v>
+        <v>9949</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5995043</t>
+          <t>https://plati.market/itm/5834250</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ImSubscribed</t>
+          <t>KappaStore</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ChatGPT Pro x5 1 месяц</t>
+          <t>[АВТОВЫДАЧА 24/7] ChatGPT 5.6 PRO 5X ПОДПИСКА / ПРОДЛЕНИЕ НА 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>9989</v>
+        <v>9969</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4695121</t>
+          <t>https://plati.market/itm/5995043</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DigiSelling</t>
+          <t>ImSubscribed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Подписка PRO x5  1 месяц</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>61</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
+          <t>ChatGPT Pro x5 1 месяц</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>9990</v>
+        <v>9989</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5162565</t>
+          <t>https://plati.market/itm/4695121</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4291,14 +4291,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Оформление подписки PRO на ваш аккаунт</t>
+          <t>Подписка PRO x5  1 месяц</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>9990</v>
@@ -4307,45 +4307,43 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5352918</t>
+          <t>https://plati.market/itm/5162565</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>forYou97</t>
+          <t>DigiSelling</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2. Активация/Продление ChatGPT Pro x5 1 МЕСЯЦ (на ваш аккаунт, быстро, без входа))</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Оформление подписки PRO на ваш аккаунт</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>9999</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4339002</t>
+          <t>https://plati.market/itm/5352918</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>forYou97</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>7. [Скидка] ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+          <t>2. Активация/Продление ChatGPT Pro x5 1 МЕСЯЦ (на ваш аккаунт, быстро, без входа))</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4353,10 +4351,8 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+      <c r="E21" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>9999</v>
@@ -4365,24 +4361,28 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5407372</t>
+          <t>https://plati.market/itm/4339002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>STORE_IZI</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>21</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
+          <t>7. [Скидка] ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F22" s="3" t="n">
         <v>9999</v>
@@ -4391,35 +4391,33 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3218237</t>
+          <t>https://plati.market/itm/5407372</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>STORE_IZI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PRO X5 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT PRO X5 1 МЕСЯЦ | Подписка / Продление (на Ваш аккаунт, с входом)</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>10064</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3235033</t>
+          <t>https://plati.market/itm/3218237</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4429,7 +4427,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT PRO X5 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
+          <t>PRO X5 1 Month | ВХОД НЕ ТРЕБУЕТСЯ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4438,26 +4436,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>10078</v>
+        <v>10064</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4371645</t>
+          <t>https://plati.market/itm/3235033</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MyKEYS</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x - 1 месяц (5.6)</t>
+          <t>Активация/Продление ChatGPT PRO X5 1 МЕСЯЦ (на ваш аккаунт, быстро, без логина, АВТО | 24/7)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4466,142 +4464,142 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10199</v>
+        <v>10078</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5992061</t>
+          <t>https://plati.market/itm/4371645</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kernel_JX</t>
+          <t>MyKEYS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[АВТО 24/7 ] ChatGPT PRO 5X 1 месяц | АКТИВАЦИЯ / ПРОДЛЕНИЕ ( без логина, на ваш аккаунт)</t>
+          <t>ChatGPT PRO 5x - 1 месяц (5.6)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>14</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>10273</v>
+        <v>10199</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3725372</t>
+          <t>https://plati.market/itm/5992061</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>princeswp</t>
+          <t>Kernel_JX</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>АВТО 24/7| Активация/ Продление CHATGPT PRO X5 на 1 месяц (Ваш аккаунт, без логина) ГАРАНТИЯ 1 МЕСЯЦ</t>
+          <t>[АВТО 24/7 ] ChatGPT PRO 5X 1 месяц | АКТИВАЦИЯ / ПРОДЛЕНИЕ ( без логина, на ваш аккаунт)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>25</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>10401</v>
+        <v>10273</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6021924</t>
+          <t>https://plati.market/itm/3725372</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VEYRO</t>
+          <t>princeswp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ ChatGPT Pro X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+          <t>АВТО 24/7| Активация/ Продление CHATGPT PRO X5 на 1 месяц (Ваш аккаунт, без логина) ГАРАНТИЯ 1 МЕСЯЦ</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>25</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>10499</v>
+        <v>10401</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4802730</t>
+          <t>https://plati.market/itm/6021924</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>northernlights</t>
+          <t>VEYRO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Подписка ChatGPT Pro 5x</t>
+          <t>АКТИВАЦИЯ ChatGPT Pro X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>35</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>10591</v>
+        <v>10499</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4380086</t>
+          <t>https://plati.market/itm/4802730</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MyKEYS</t>
+          <t>northernlights</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x - 1 месяц (5.5)</t>
+          <t>Подписка ChatGPT Pro 5x</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4610,26 +4608,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>10599</v>
+        <v>10591</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3705934</t>
+          <t>https://plati.market/itm/4380086</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hayta</t>
+          <t>MyKEYS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3. 24/7 АВТО | ChatGPT PRO X5 1 МЕСЯЦ | Подписка (на Ваш аккаунт, без входа, за минуту)</t>
+          <t>ChatGPT PRO 5x - 1 месяц (5.5)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4638,26 +4636,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10735</v>
+        <v>10599</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5794510</t>
+          <t>https://plati.market/itm/3705934</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BuyForGame</t>
+          <t>hayta</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[БЕЗ ВХОДА] АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | ЗА МИНУТУ | НА ВАШ АККАУНТ |</t>
+          <t>3. 24/7 АВТО | ChatGPT PRO X5 1 МЕСЯЦ | Подписка (на Ваш аккаунт, без входа, за минуту)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4666,65 +4664,65 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>10899</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5214484</t>
+          <t>https://plati.market/itm/5794510</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>BuyForGame</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] на 1 месяц – активация на ваш аккаунт (с передачей логина и пароля, со входом)</t>
+          <t>[БЕЗ ВХОДА] АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | ЗА МИНУТУ | НА ВАШ АККАУНТ |</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>27</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>10999</v>
+        <v>10899</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4313142</t>
+          <t>https://plati.market/itm/5214484</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ProSeller.inc</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2. PRO 5x (1 месяц)</t>
+          <t>[ChatGPT PRO 5x] на 1 месяц – активация на ваш аккаунт (с передачей логина и пароля, со входом)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>65</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F34" s="3" t="n">
         <v>10999</v>
@@ -4733,17 +4731,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4481462</t>
+          <t>https://plati.market/itm/4313142</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>ProSeller.inc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] - купить/продлить на ваш аккаунт - 1 мес - со входом (логин+пароль) [РУЧНАЯ]</t>
+          <t>2. PRO 5x (1 месяц)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4752,26 +4750,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>11199</v>
+        <v>10999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5807701</t>
+          <t>https://plati.market/itm/4481462</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mahoraga borz</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Продление \ ChatGPT Pro x5 на 1 месяц (на ваш аккаунт, без входа в аккаунт)</t>
+          <t>[ChatGPT PRO 5x] - купить/продлить на ваш аккаунт - 1 мес - со входом (логин+пароль) [РУЧНАЯ]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4780,138 +4778,138 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>11205</v>
+        <v>11199</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5980351</t>
+          <t>https://plati.market/itm/5807701</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IGROKLAD</t>
+          <t>Mahoraga borz</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ChatGPT PRO [ НА 1 МЕСЯЦ ]</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
+          <t>Продление \ ChatGPT Pro x5 на 1 месяц (на ваш аккаунт, без входа в аккаунт)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>11345</v>
+        <v>11205</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3859725</t>
+          <t>https://plati.market/itm/5980351</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fursov.me</t>
+          <t>IGROKLAD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GPT PRO X5 &gt;&gt; Новый аккаунт + Почта (1 месяц)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT PRO [ НА 1 МЕСЯЦ ]</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>11349</v>
+        <v>11345</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6063721</t>
+          <t>https://plati.market/itm/3859725</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MORPHEUSINTELLIGENCE</t>
+          <t>fursov.me</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5X</t>
+          <t>GPT PRO X5 &gt;&gt; Новый аккаунт + Почта (1 месяц)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>54</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>11390</v>
+        <v>11349</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3648532</t>
+          <t>https://plati.market/itm/6063721</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UgolokH</t>
+          <t>MORPHEUSINTELLIGENCE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PRO X5</t>
+          <t>ChatGPT Pro 5X</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>11490</v>
+        <v>11390</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5481303</t>
+          <t>https://plati.market/itm/3648532</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>UgolokH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 1 месяц (код активации)</t>
+          <t>PRO X5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4919,115 +4917,113 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+      <c r="E41" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>11749</v>
+        <v>11490</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5424895</t>
+          <t>https://plati.market/itm/5481303</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AppStops</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pro подписка на месяц</t>
+          <t>ChatGPT PRO X5 1 месяц (код активации)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>скрыто</t>
+          <t>&gt;100</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>11790</v>
+        <v>11749</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6055394</t>
+          <t>https://plati.market/itm/5424895</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MisterHeisenberg</t>
+          <t>AppStops</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT PRO x5 1 МЕСЯЦ на ваш аккаунт</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
+          <t>Pro подписка на месяц</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>11800</v>
+        <v>11790</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4339392</t>
+          <t>https://plati.market/itm/6055394</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MARCEL VPN</t>
+          <t>MisterHeisenberg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2.АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Pro X5 — 1 МЕСЯЦ |  НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Активация/Продление ChatGPT PRO x5 1 МЕСЯЦ на ваш аккаунт</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>11889</v>
+        <v>11800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4756087</t>
+          <t>https://plati.market/itm/4339392</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IronMarvell</t>
+          <t>MARCEL VPN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x 1 месяц</t>
+          <t>2.АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT Pro X5 — 1 МЕСЯЦ |  НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5035,353 +5031,357 @@
           <t>&gt;100</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>11990</v>
+        <v>11889</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4616358</t>
+          <t>https://plati.market/itm/4756087</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>E-Treasure</t>
+          <t>IronMarvell</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[ChatGPT PRO 5x] готовый аккаунт с подпиской + почта на 1 месяц</t>
+          <t>ChatGPT PRO 5x 1 месяц</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>11999</v>
+        <v>11990</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3931351</t>
+          <t>https://plati.market/itm/4616358</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>furfur</t>
+          <t>E-Treasure</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 1 месяц x5</t>
+          <t>[ChatGPT PRO 5x] готовый аккаунт с подпиской + почта на 1 месяц</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>2</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12002</v>
+        <v>11999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6063473</t>
+          <t>https://plati.market/itm/3931351</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>of_existence</t>
+          <t>furfur</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
+          <t>ChatGPT PRO 1 месяц x5</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12068</v>
+        <v>12002</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4853415</t>
+          <t>https://plati.market/itm/6063473</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Super Man</t>
+          <t>of_existence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>АКТИВАЦИЯ / ПРОДЛЕНИЕ ChatGPT PRO X5 — 1 МЕСЯЦ | НА ВАШ АККАУНТ</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>12100</v>
+        <v>12068</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5361993</t>
+          <t>https://plati.market/itm/4853415</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZaruBot</t>
+          <t>Super Man</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x 1 месяц {Для старых и новых (обеих) учетных записей {Продление}</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>24</v>
+          <t>ChatGPT PRO X5</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>12269</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5865073</t>
+          <t>https://plati.market/itm/5361993</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Genixai</t>
+          <t>ZaruBot</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4: ChatGPT Pro 5X | Активация на ваш Email | Высокие лимиты | Полная гарантия</t>
+          <t>ChatGPT PRO 5x 1 месяц {Для старых и новых (обеих) учетных записей {Продление}</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>12279</v>
+        <v>12269</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5931604</t>
+          <t>https://plati.market/itm/5865073</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MrKronos</t>
+          <t>Genixai</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5x</t>
+          <t>4: ChatGPT Pro 5X | Активация на ваш Email | Высокие лимиты | Полная гарантия</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>12290</v>
+        <v>12279</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5849306</t>
+          <t>https://plati.market/itm/5931604</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JensenLoantos</t>
+          <t>MrKronos</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ChatGPT Pro на 1 месяц без входа в систему</t>
+          <t>ChatGPT PRO 5x</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>12318</v>
+        <v>12290</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4362367</t>
+          <t>https://plati.market/itm/5849306</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AccountBroker</t>
+          <t>JensenLoantos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.Активация/Продление ChatGPT Pro 5x 1 МЕСЯЦ (Без входа с использованием файлов cookie)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT Pro на 1 месяц без входа в систему</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>12469</v>
+        <v>12318</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5897564</t>
+          <t>https://plati.market/itm/4362367</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ai_Box</t>
+          <t>AccountBroker</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pro 5X [ ЛУЧШАЯ ЦЕНА ]</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>121</v>
-      </c>
-      <c r="E55" t="n">
-        <v>7</v>
+          <t>3.Активация/Продление ChatGPT Pro 5x 1 МЕСЯЦ (Без входа с использованием файлов cookie)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>12584</v>
+        <v>12469</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3683609</t>
+          <t>https://plati.market/itm/5897564</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>_RenS_</t>
+          <t>Ai_Box</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>У меня уже есть аккаунт ChatGPT (оформляется подписка Pro без входа в аккаунт)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Pro 5X [ ЛУЧШАЯ ЦЕНА ]</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>121</v>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>12609</v>
+        <v>12584</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6057697</t>
+          <t>https://plati.market/itm/3683609</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SubVault</t>
+          <t>_RenS_</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Activation/Renewal ChatGPT Pro 5X – 1 месяц | Высокие лимиты | На ваш Email | Требуется вход</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0</v>
+          <t>У меня уже есть аккаунт ChatGPT (оформляется подписка Pro без входа в аккаунт)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>12640</v>
+        <v>12609</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5960360</t>
+          <t>https://plati.market/itm/6057697</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Subverse</t>
+          <t>SubVault</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 5x • Официальный доступ • Полная гарантия</t>
+          <t>Activation/Renewal ChatGPT Pro 5X – 1 месяц | Высокие лимиты | На ваш Email | Требуется вход</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -5391,49 +5391,49 @@
         <v>0</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>12651</v>
+        <v>12640</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5873793</t>
+          <t>https://plati.market/itm/5960360</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>88Store AI</t>
+          <t>Subverse</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PRO x5 - 1 MONTH</t>
+          <t>ChatGPT Pro 5x • Официальный доступ • Полная гарантия</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>12717</v>
+        <v>12651</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5763830</t>
+          <t>https://plati.market/itm/5873793</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PickBest</t>
+          <t>88Store AI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chat GPT  Pro 5x | 1 Month | On your Account | Ready Account</t>
+          <t>PRO x5 - 1 MONTH</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -5443,326 +5443,324 @@
         <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>13119</v>
+        <v>12717</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6052016</t>
+          <t>https://plati.market/itm/5763830</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DigiMari</t>
+          <t>PickBest</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Активация / Продление ChatGPT PRO - 1 МЕС | ВАШ Аккаунт</t>
+          <t>Chat GPT  Pro 5x | 1 Month | On your Account | Ready Account</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>13153</v>
+        <v>13119</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5998486</t>
+          <t>https://plati.market/itm/6052016</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VantaStore</t>
+          <t>DigiMari</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ChatGPT Pro x5 - 1 месяц</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>Активация / Продление ChatGPT PRO - 1 МЕС | ВАШ Аккаунт</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>13277</v>
+        <v>13153</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3964931</t>
+          <t>https://plati.market/itm/5998486</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AI GUO GUO</t>
+          <t>VantaStore</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+          <t>ChatGPT Pro x5 - 1 месяц</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>&gt;100</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>2</v>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>13340</v>
+        <v>13277</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5990295</t>
+          <t>https://plati.market/itm/3964931</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PROMARKET88</t>
+          <t>AI GUO GUO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GPT PRO</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
+          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
         <v>2</v>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
       <c r="F64" s="3" t="n">
-        <v>13402</v>
+        <v>13340</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5869102</t>
+          <t>https://plati.market/itm/5990295</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AI GUO GUO</t>
+          <t>PROMARKET88</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+          <t>GPT PRO</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>13512</v>
+        <v>13402</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4724944</t>
+          <t>https://plati.market/itm/5869102</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>AI GUO GUO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Без Входа)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT-Pro x5 (1 МЕСЯЦ)</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>212</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>13667</v>
+        <v>13512</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5465686</t>
+          <t>https://plati.market/itm/4724944</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DerdoArt</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pro x5</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>54</v>
+          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Без Входа)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>14159</v>
+        <v>13667</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5688276</t>
+          <t>https://plati.market/itm/5465686</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lyutsik_Shop</t>
+          <t>DerdoArt</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CHATGPT 5.2 PRO 1 месяц ПОДПИСКА С ЗАХОДОМ НА ВАШ АККАУНТ</t>
+          <t>Pro x5</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>14229</v>
+        <v>14159</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5981988</t>
+          <t>https://plati.market/itm/5688276</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HunterGPT</t>
+          <t>Lyutsik_Shop</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 5X — 1 МЕСЯЦ (Требуется вход в аккаунт | 24/7)</t>
+          <t>CHATGPT 5.2 PRO 1 месяц ПОДПИСКА С ЗАХОДОМ НА ВАШ АККАУНТ</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>14326</v>
+        <v>14229</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/6002830</t>
+          <t>https://plati.market/itm/5981988</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>67_Shop</t>
+          <t>HunterGPT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ChatGPT PRO 5X — 1 месяц | На ваш аккаунт | Без входа</t>
+          <t>Активация/Продление ChatGPT Pro 5X — 1 МЕСЯЦ (Требуется вход в аккаунт | 24/7)</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>14981</v>
+        <v>14326</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3636620</t>
+          <t>https://plati.market/itm/6002830</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>hmmml</t>
+          <t>67_Shop</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>4. ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
+          <t>ChatGPT PRO 5X — 1 месяц | На ваш аккаунт | Без входа</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>26655</v>
+        <v>39</v>
       </c>
       <c r="E71" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>14999</v>
+        <v>14981</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4183350</t>
+          <t>https://plati.market/itm/3636620</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SOFT_OPTOM</t>
+          <t>hmmml</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CHATGPT Pro 1 месяц БЫСТРО x5</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>4. ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>26655</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>14999</v>
@@ -5771,17 +5769,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5651002</t>
+          <t>https://plati.market/itm/4183350</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>starfast</t>
+          <t>SOFT_OPTOM</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ChatGPT Pro X5 - на 1 Месяц</t>
+          <t>CHATGPT Pro 1 месяц БЫСТРО x5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5793,23 +5791,23 @@
         <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>15399</v>
+        <v>14999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5401296</t>
+          <t>https://plati.market/itm/5651002</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>tuanbes</t>
+          <t>starfast</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
+          <t>ChatGPT Pro X5 - на 1 Месяц</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5818,292 +5816,292 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>15434</v>
+        <v>15399</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5884270</t>
+          <t>https://plati.market/itm/5401296</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ProSeller.inc</t>
+          <t>tuanbes</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2. PRO 5x (1 месяц)</t>
+          <t>ChatGPT PRO X5 НА 1 МЕСЯЦ (персональный аккаунт + почта)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>скрыто</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>скрыто</t>
-        </is>
+          <t>&gt;100</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>15799</v>
+        <v>15434</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4591665</t>
+          <t>https://plati.market/itm/5884270</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FoxyPayGlobal</t>
+          <t>ProSeller.inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pro | Месяц  | 1 участник</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>13</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
+          <t>2. PRO 5x (1 месяц)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>скрыто</t>
+        </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>16049</v>
+        <v>15799</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5877715</t>
+          <t>https://plati.market/itm/4591665</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DanyCyber</t>
+          <t>FoxyPayGlobal</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Активация/продление подписки ChatGPT Pro 5 раз по 1 месяц</t>
+          <t>Pro | Месяц  | 1 участник</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>16179</v>
+        <v>16049</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5437983</t>
+          <t>https://plati.market/itm/5877715</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1Subs</t>
+          <t>DanyCyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Требуется Вход)</t>
+          <t>Активация/продление подписки ChatGPT Pro 5 раз по 1 месяц</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>16246</v>
+        <v>16179</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5087858</t>
+          <t>https://plati.market/itm/5437983</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FUNFINITY SHOP</t>
+          <t>1Subs</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pro 1 Месяц (x5)</t>
+          <t>Апгрейд/Продление: ChatGPT Pro 5x - 1 Месяц (Требуется Вход)</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>16516</v>
+        <v>16246</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5870331</t>
+          <t>https://plati.market/itm/5087858</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>karlincards</t>
+          <t>FUNFINITY SHOP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>НОВАЯ учетная запись ChatGPT PRO X5 1 МЕСЯЦ (новая учетная запись с доступом к электронной почте)</t>
+          <t>Pro 1 Месяц (x5)</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>19554</v>
+        <v>16516</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5660318</t>
+          <t>https://plati.market/itm/5870331</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>sashasale</t>
+          <t>karlincards</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Активация/Продление ChatGPT Pro 20x 1 месяц (Без Входа)</t>
+          <t>НОВАЯ учетная запись ChatGPT PRO X5 1 МЕСЯЦ (новая учетная запись с доступом к электронной почте)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>19899</v>
+        <v>19554</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5559857</t>
+          <t>https://plati.market/itm/5660318</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AltSubs</t>
+          <t>sashasale</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ChatGPT Pro - 1 месяц: новый аккаунт (полный доступ)</t>
+          <t>Активация/Продление ChatGPT Pro 20x 1 месяц (Без Входа)</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>21403</v>
+        <v>19899</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5144685</t>
+          <t>https://plati.market/itm/5559857</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>D.O.G.E. PRIME SHOP</t>
+          <t>AltSubs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pro (1 месяц)</t>
+          <t>ChatGPT Pro - 1 месяц: новый аккаунт (полный доступ)</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>21809</v>
+        <v>21403</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/3714311</t>
+          <t>https://plati.market/itm/5144685</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Luxtake</t>
+          <t>D.O.G.E. PRIME SHOP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3. 24/7 АВТО | Продление ChatGPT PRO — 1 МЕСЯЦ | На Ваш аккаунт | Без входа | За минуту</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>Pro (1 месяц)</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>21975</v>
+        <v>21809</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5231895</t>
+          <t>https://plati.market/itm/3714311</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PREMIUMSTOREXYZ</t>
+          <t>Luxtake</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pro (1 месяц)</t>
+          <t>3. 24/7 АВТО | Продление ChatGPT PRO — 1 МЕСЯЦ | На Ваш аккаунт | Без входа | За минуту</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6112,172 +6110,200 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>22183</v>
+        <v>21975</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/4881173</t>
+          <t>https://plati.market/itm/5231895</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Exclusive_Play</t>
+          <t>PREMIUMSTOREXYZ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pro</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>33</v>
+          <t>Pro (1 месяц)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>25475</v>
+        <v>22183</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5414735</t>
+          <t>https://plati.market/itm/4881173</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sneelipo_615</t>
+          <t>Exclusive_Play</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ChatGPT PRO x20 1 месяц</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>25983</v>
+        <v>25475</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5696109</t>
+          <t>https://plati.market/itm/5414735</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OnePayNow</t>
+          <t>Sneelipo_615</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ChatGPT Pro 1 месяц</t>
+          <t>ChatGPT PRO x20 1 месяц</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>26951</v>
+        <v>25983</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5290688</t>
+          <t>https://plati.market/itm/5696109</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pro Digital Goods</t>
+          <t>OnePayNow</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1 месяц ChatGPT PRO</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>&gt;100</t>
-        </is>
+          <t>ChatGPT Pro 1 месяц</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>14</v>
       </c>
       <c r="E89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>28063</v>
+        <v>26951</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>https://plati.market/itm/5777882</t>
+          <t>https://plati.market/itm/5290688</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>vvlstl</t>
+          <t>Pro Digital Goods</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pro (месяц)</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
+          <t>1 месяц ChatGPT PRO</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>&gt;100</t>
+        </is>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>29405</v>
+        <v>28063</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>https://plati.market/itm/5777882</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>vvlstl</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Pro (месяц)</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>29405</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
           <t>https://plati.market/itm/4796860</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>SjMarket</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>1 месяц PRO</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D92" t="n">
         <v>12</v>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="n">
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
         <v>34990</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F91"/>
+  <autoFilter ref="A1:F92"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
@@ -6369,6 +6395,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
